--- a/outputs/q3/material_share.xlsx
+++ b/outputs/q3/material_share.xlsx
@@ -475,25 +475,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>28200</v>
+        <v>24450.93165669303</v>
       </c>
       <c r="C2" t="n">
-        <v>23411.38583333334</v>
+        <v>16825.64960818229</v>
       </c>
       <c r="D2" t="n">
-        <v>0.830190986997636</v>
+        <v>0.6881394068915387</v>
       </c>
       <c r="E2" t="n">
-        <v>4723.031874999996</v>
+        <v>6963.462974272889</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2847933596986992</v>
       </c>
       <c r="G2" t="n">
-        <v>65.58229166666666</v>
+        <v>661.8190742378504</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.02706723340976206</v>
       </c>
     </row>
     <row r="3">
@@ -501,25 +501,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>28200</v>
+        <v>22590.59415349913</v>
       </c>
       <c r="C3" t="n">
-        <v>23411.38583333334</v>
+        <v>12916.29972601027</v>
       </c>
       <c r="D3" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5717556447717258</v>
       </c>
       <c r="E3" t="n">
-        <v>4723.031874999996</v>
+        <v>7837.257756701569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.3469257029473761</v>
       </c>
       <c r="G3" t="n">
-        <v>65.58229166666666</v>
+        <v>1837.03667078729</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.0813186522808983</v>
       </c>
     </row>
     <row r="4">
@@ -527,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>28200</v>
+        <v>23755.14895769007</v>
       </c>
       <c r="C4" t="n">
-        <v>23411.38583333334</v>
+        <v>13790.13426288963</v>
       </c>
       <c r="D4" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5805113782890198</v>
       </c>
       <c r="E4" t="n">
-        <v>4723.031874999996</v>
+        <v>7944.113948425201</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.334416507451683</v>
       </c>
       <c r="G4" t="n">
-        <v>65.58229166666666</v>
+        <v>2020.900746375234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.08507211425929716</v>
       </c>
     </row>
     <row r="5">
@@ -553,25 +553,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>28200</v>
+        <v>22590.27438766167</v>
       </c>
       <c r="C5" t="n">
-        <v>23411.38583333334</v>
+        <v>13325.2896323813</v>
       </c>
       <c r="D5" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5898684276123396</v>
       </c>
       <c r="E5" t="n">
-        <v>4723.031874999996</v>
+        <v>7420.73115998389</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.3284922986166532</v>
       </c>
       <c r="G5" t="n">
-        <v>65.58229166666666</v>
+        <v>1844.253595296483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.0816392737710072</v>
       </c>
     </row>
     <row r="6">
@@ -579,25 +579,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>28200</v>
+        <v>23910.31077613482</v>
       </c>
       <c r="C6" t="n">
-        <v>23411.38583333334</v>
+        <v>13951.8854317202</v>
       </c>
       <c r="D6" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5835091631534023</v>
       </c>
       <c r="E6" t="n">
-        <v>4723.031874999996</v>
+        <v>7938.355159407394</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.3320055198668002</v>
       </c>
       <c r="G6" t="n">
-        <v>65.58229166666666</v>
+        <v>2020.070185007217</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.08448531697979747</v>
       </c>
     </row>
     <row r="7">
@@ -605,25 +605,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>28200</v>
+        <v>25402.84154834821</v>
       </c>
       <c r="C7" t="n">
-        <v>23411.38583333334</v>
+        <v>14171.14663173271</v>
       </c>
       <c r="D7" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5578567501891998</v>
       </c>
       <c r="E7" t="n">
-        <v>4723.031874999996</v>
+        <v>8318.774114199949</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.3274741567146006</v>
       </c>
       <c r="G7" t="n">
-        <v>65.58229166666666</v>
+        <v>2912.920802415549</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.1146690930961996</v>
       </c>
     </row>
     <row r="8">
@@ -631,25 +631,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>28200</v>
+        <v>25222.92359598352</v>
       </c>
       <c r="C8" t="n">
-        <v>23411.38583333334</v>
+        <v>13968.74584683005</v>
       </c>
       <c r="D8" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5538115275841545</v>
       </c>
       <c r="E8" t="n">
-        <v>4723.031874999996</v>
+        <v>7470.739209755945</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2961884724158455</v>
       </c>
       <c r="G8" t="n">
-        <v>65.58229166666666</v>
+        <v>3783.438539397529</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9">
@@ -657,25 +657,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>28200</v>
+        <v>25191.98690114533</v>
       </c>
       <c r="C9" t="n">
-        <v>23411.38583333334</v>
+        <v>14005.20068503416</v>
       </c>
       <c r="D9" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5559387093995918</v>
       </c>
       <c r="E9" t="n">
-        <v>4723.031874999996</v>
+        <v>7407.988180939375</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2940612906004082</v>
       </c>
       <c r="G9" t="n">
-        <v>65.58229166666666</v>
+        <v>3778.798035171799</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.1499999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -683,25 +683,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>28200</v>
+        <v>26323.57611436056</v>
       </c>
       <c r="C10" t="n">
-        <v>23411.38583333334</v>
+        <v>14899.83029296825</v>
       </c>
       <c r="D10" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5660260683517008</v>
       </c>
       <c r="E10" t="n">
-        <v>4723.031874999996</v>
+        <v>7475.209404238228</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2839739316482992</v>
       </c>
       <c r="G10" t="n">
-        <v>65.58229166666666</v>
+        <v>3948.536417154084</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -709,25 +709,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>28200</v>
+        <v>25570.12463099577</v>
       </c>
       <c r="C11" t="n">
-        <v>23411.38583333334</v>
+        <v>14540.79944681819</v>
       </c>
       <c r="D11" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5686636125813802</v>
       </c>
       <c r="E11" t="n">
-        <v>4723.031874999996</v>
+        <v>7193.80648952822</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2813363874186198</v>
       </c>
       <c r="G11" t="n">
-        <v>65.58229166666666</v>
+        <v>3835.518694649365</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
@@ -735,25 +735,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>28200</v>
+        <v>26516.75169659503</v>
       </c>
       <c r="C12" t="n">
-        <v>23411.38583333334</v>
+        <v>15060.97486499312</v>
       </c>
       <c r="D12" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5679796317935529</v>
       </c>
       <c r="E12" t="n">
-        <v>4723.031874999996</v>
+        <v>7478.26407711266</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.282020368206447</v>
       </c>
       <c r="G12" t="n">
-        <v>65.58229166666666</v>
+        <v>3977.512754489255</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13">
@@ -761,25 +761,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>28200</v>
+        <v>26165.74503300766</v>
       </c>
       <c r="C13" t="n">
-        <v>23411.38583333334</v>
+        <v>14854.99167195739</v>
       </c>
       <c r="D13" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5677266843813565</v>
       </c>
       <c r="E13" t="n">
-        <v>4723.031874999996</v>
+        <v>7385.891606099127</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2822733156186435</v>
       </c>
       <c r="G13" t="n">
-        <v>65.58229166666666</v>
+        <v>3924.861754951148</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="14">
@@ -787,25 +787,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>28200</v>
+        <v>27278.18830695096</v>
       </c>
       <c r="C14" t="n">
-        <v>23411.38583333334</v>
+        <v>15663.56794854499</v>
       </c>
       <c r="D14" t="n">
-        <v>0.830190986997636</v>
+        <v>0.574215844992669</v>
       </c>
       <c r="E14" t="n">
-        <v>4723.031874999996</v>
+        <v>7522.892112363328</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.275784155007331</v>
       </c>
       <c r="G14" t="n">
-        <v>65.58229166666666</v>
+        <v>4091.728246042645</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="15">
@@ -813,25 +813,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>28200</v>
+        <v>27728.20874072676</v>
       </c>
       <c r="C15" t="n">
-        <v>23411.38583333334</v>
+        <v>15365.77926311073</v>
       </c>
       <c r="D15" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5541569384012071</v>
       </c>
       <c r="E15" t="n">
-        <v>4723.031874999996</v>
+        <v>8203.198166507018</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.295843061598793</v>
       </c>
       <c r="G15" t="n">
-        <v>65.58229166666666</v>
+        <v>4159.231311109013</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="16">
@@ -839,25 +839,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>28200</v>
+        <v>26683.18299404287</v>
       </c>
       <c r="C16" t="n">
-        <v>23411.38583333334</v>
+        <v>15222.79535767435</v>
       </c>
       <c r="D16" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5705014788180596</v>
       </c>
       <c r="E16" t="n">
-        <v>4723.031874999996</v>
+        <v>7457.910187262083</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2794985211819405</v>
       </c>
       <c r="G16" t="n">
-        <v>65.58229166666666</v>
+        <v>4002.47744910643</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17">
@@ -865,25 +865,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>28200</v>
+        <v>25586.71918379265</v>
       </c>
       <c r="C17" t="n">
-        <v>23411.38583333334</v>
+        <v>14362.28990619134</v>
       </c>
       <c r="D17" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5613181511480699</v>
       </c>
       <c r="E17" t="n">
-        <v>4723.031874999996</v>
+        <v>7386.421400032409</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2886818488519301</v>
       </c>
       <c r="G17" t="n">
-        <v>65.58229166666666</v>
+        <v>3838.007877568896</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="18">
@@ -891,25 +891,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>28200</v>
+        <v>26367.44471828533</v>
       </c>
       <c r="C18" t="n">
-        <v>23411.38583333334</v>
+        <v>15197.81517841622</v>
       </c>
       <c r="D18" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5763855899118211</v>
       </c>
       <c r="E18" t="n">
-        <v>4723.031874999996</v>
+        <v>7214.512832126305</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2736144100881788</v>
       </c>
       <c r="G18" t="n">
-        <v>65.58229166666666</v>
+        <v>3955.116707742799</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="19">
@@ -917,25 +917,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>28200</v>
+        <v>28841.61004419722</v>
       </c>
       <c r="C19" t="n">
-        <v>23411.38583333334</v>
+        <v>17251.89288144741</v>
       </c>
       <c r="D19" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5981598411118662</v>
       </c>
       <c r="E19" t="n">
-        <v>4723.031874999996</v>
+        <v>7263.475656120224</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2518401588881338</v>
       </c>
       <c r="G19" t="n">
-        <v>65.58229166666666</v>
+        <v>4326.241506629583</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="20">
@@ -943,25 +943,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>28200</v>
+        <v>27650.32018527477</v>
       </c>
       <c r="C20" t="n">
-        <v>23411.38583333334</v>
+        <v>16047.64997674625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5803784502029908</v>
       </c>
       <c r="E20" t="n">
-        <v>4723.031874999996</v>
+        <v>7455.122180737309</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2696215497970091</v>
       </c>
       <c r="G20" t="n">
-        <v>65.58229166666666</v>
+        <v>4147.548027791216</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="21">
@@ -969,25 +969,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>28200</v>
+        <v>26063.64474106493</v>
       </c>
       <c r="C21" t="n">
-        <v>23411.38583333334</v>
+        <v>15066.40564490694</v>
       </c>
       <c r="D21" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5780621165837508</v>
       </c>
       <c r="E21" t="n">
-        <v>4723.031874999996</v>
+        <v>7087.692384998252</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2719378834162492</v>
       </c>
       <c r="G21" t="n">
-        <v>65.58229166666666</v>
+        <v>3909.546711159739</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22">
@@ -995,25 +995,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>28200</v>
+        <v>27281.12154947827</v>
       </c>
       <c r="C22" t="n">
-        <v>23411.38583333334</v>
+        <v>15943.55864126961</v>
       </c>
       <c r="D22" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5844172723014212</v>
       </c>
       <c r="E22" t="n">
-        <v>4723.031874999996</v>
+        <v>7245.394675786921</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2655827276985789</v>
       </c>
       <c r="G22" t="n">
-        <v>65.58229166666666</v>
+        <v>4092.16823242174</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="23">
@@ -1021,25 +1021,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>28200</v>
+        <v>26495.63917463225</v>
       </c>
       <c r="C23" t="n">
-        <v>23411.38583333334</v>
+        <v>15248.9688986254</v>
       </c>
       <c r="D23" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5755274971145153</v>
       </c>
       <c r="E23" t="n">
-        <v>4723.031874999996</v>
+        <v>7272.324399812008</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2744725028854845</v>
       </c>
       <c r="G23" t="n">
-        <v>65.58229166666666</v>
+        <v>3974.345876194837</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="24">
@@ -1047,25 +1047,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>28200</v>
+        <v>26454.62579509146</v>
       </c>
       <c r="C24" t="n">
-        <v>23411.38583333334</v>
+        <v>15290.15536106299</v>
       </c>
       <c r="D24" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5779766260727081</v>
       </c>
       <c r="E24" t="n">
-        <v>4723.031874999996</v>
+        <v>7196.276564764743</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2720233739272918</v>
       </c>
       <c r="G24" t="n">
-        <v>65.58229166666666</v>
+        <v>3968.193869263718</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="25">
@@ -1073,25 +1073,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>28200</v>
+        <v>26278.08511434772</v>
       </c>
       <c r="C25" t="n">
-        <v>23411.38583333334</v>
+        <v>14771.35143039466</v>
       </c>
       <c r="D25" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5621167359081873</v>
       </c>
       <c r="E25" t="n">
-        <v>4723.031874999996</v>
+        <v>7565.020916800893</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1674833998226949</v>
+        <v>0.2878832640918126</v>
       </c>
       <c r="G25" t="n">
-        <v>65.58229166666666</v>
+        <v>3941.712767152157</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
